--- a/whitefiber/docs/reports/20261022_whitefiber_v0.2_TK同步.xlsx
+++ b/whitefiber/docs/reports/20261022_whitefiber_v0.2_TK同步.xlsx
@@ -7131,7 +7131,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -7169,25 +7169,30 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>單位／FY26</t>
+          <t>單位</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>FY26</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
           <t>FY27</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>FY28</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>FY29</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>FY30</t>
         </is>
@@ -7216,6 +7221,9 @@
       <c r="F3" t="n">
         <v>0.181302608379369</v>
       </c>
+      <c r="G3" t="n">
+        <v>0.170650440492906</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -7240,6 +7248,9 @@
       <c r="F4" t="n">
         <v>0.302171013965614</v>
       </c>
+      <c r="G4" t="n">
+        <v>0.28441740082151</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -7264,6 +7275,9 @@
       <c r="F5" t="n">
         <v>0.379130530699714</v>
       </c>
+      <c r="G5" t="n">
+        <v>0.356108917980401</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7288,6 +7302,9 @@
       <c r="F6" t="n">
         <v>0.379130530699714</v>
       </c>
+      <c r="G6" t="n">
+        <v>0.356108917980401</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -7312,6 +7329,9 @@
       <c r="F7" t="n">
         <v>0.379130530699714</v>
       </c>
+      <c r="G7" t="n">
+        <v>0.356108917980401</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -7372,6 +7392,9 @@
       <c r="F10" t="n">
         <v>0.248810499373958</v>
       </c>
+      <c r="G10" t="n">
+        <v>0.252948412382418</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -7396,6 +7419,9 @@
       <c r="F11" t="n">
         <v>0.156942007297419</v>
       </c>
+      <c r="G11" t="n">
+        <v>0.159552075502756</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -7419,6 +7445,9 @@
       </c>
       <c r="F12" t="n">
         <v>0.340041015811076</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.345696163589304</v>
       </c>
     </row>
   </sheetData>
